--- a/input/mapping/033. OCB_GOLD_TCKH_V_TB_AR_DTL_BDH_PHAT.xlsx
+++ b/input/mapping/033. OCB_GOLD_TCKH_V_TB_AR_DTL_BDH_PHAT.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OCB\Zone_C\Code dev lại silver\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="567" documentId="13_ncr:1_{AB9DA439-EF4D-476D-A1DB-360185071422}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{435DFA29-6CFB-4CBD-A1A1-8EB00BAA8BE7}"/>
+  <xr:revisionPtr revIDLastSave="581" documentId="13_ncr:1_{AB9DA439-EF4D-476D-A1DB-360185071422}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BFBC8370-10DE-4BDE-AE77-014D552BC397}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="3" r:id="rId1"/>
@@ -972,9 +972,14 @@
 LEFT JOIN V_BRANCH_LIST B ON Z3.BRANCH_CODE = B.BRANCH_CODE;</t>
   </si>
   <si>
-    <t>USE CATALOG IDENTIFIER(:curated);
+    <t xml:space="preserve">USE CATALOG IDENTIFIER(:curated);
 USE SCHEMA tckh;
-CREATE OR REPLACE TABLE holiday AS
+INSERT OVERWRITE holiday (
+    DATA_DATE_DT,
+    HOLIDAY_DATE_DT,
+    DATA_DT,
+    HOLIDAY_DT
+)
 SELECT
     TO_DATE(CAST(MAX(W.msr_prd_id) AS STRING), 'yyyyMMdd')   AS DATA_DATE_DT,
     TO_DATE(CAST(D.msr_prd_id AS STRING), 'yyyyMMdd')        AS HOLIDAY_DATE_DT,
@@ -985,12 +990,21 @@
     ON  D.msr_prd_id &gt; W.msr_prd_id
     AND W.bsn_day_f = 1
 WHERE D.bsn_day_f = 0
-GROUP BY D.msr_prd_id;</t>
+GROUP BY D.msr_prd_id;
+</t>
   </si>
   <si>
     <t xml:space="preserve">USE CATALOG IDENTIFIER(:curated);
 USE SCHEMA tckh;
-CREATE OR REPLACE TABLE working_day AS
+INSERT OVERWRITE working_day (
+    DATA_DT,
+    FROM_DATE_DT,
+    FROM_DT,
+    END_DT,
+    END_DATE_DT,
+    BEGIN_OF_MONTH,
+    BEGIN_OF_MONTH_DATE
+)
 WITH
 v_from_dt AS (
     SELECT
@@ -1074,28 +1088,9 @@
   <si>
     <t>USE CATALOG IDENTIFIER(:curated);
 USE SCHEMA tckh;
-CREATE TABLE IF NOT EXISTS CB_OU_DIM (
-    OU_DIM_ID       BIGINT,     -- MAX(OU_DIM_ID) + ROW_NUMBER()
-    OU_ID           STRING,     -- branch_hashkey (SHA256)
-    OU_NM           STRING,
-    OU_CODE         STRING,
-    PRN_OU_ID       STRING,
-    PRN_OU_NM       STRING,
-    PRN_OU_CODE     STRING,
-    CB_AREA_ID      INTEGER,
-    CB_AREA_NM      STRING,
-    CRT_TM          TIMESTAMP,
-    EFF_FM_DT       DATE,
-    EFF_TO_DT       DATE,
-    START_WK_DT     DATE,
-    OU_ADR          STRING,
-    OU_PH           STRING
-)
-USING DELTA;
 MERGE INTO CB_OU_DIM tgt
 USING (
     WITH
-    -- STS Hub: khóa có trạng thái mới nhất = 'D' (đã xóa) đến :etl_date
     sts_deleted AS (
         SELECT branch_hashkey
         FROM IDENTIFIER(:cleaned || '.raw_vault.sts_hub_branch')
@@ -1103,15 +1098,12 @@
         GROUP BY branch_hashkey
         HAVING MAX_BY(cdc_status, source_event_date) = 'D'
     ),
-    -- Hub đang có hiệu lực = Hub LEFT JOIN loại các khóa deleted
     hub_active AS (
         SELECT h.branch_hashkey, h.business_key, h.source_event_date
         FROM IDENTIFIER(:cleaned || '.raw_vault.hub_branch') h
-        LEFT JOIN sts_deleted d
-            ON h.branch_hashkey = d.branch_hashkey
+        LEFT JOIN sts_deleted d ON h.branch_hashkey = d.branch_hashkey
         WHERE d.branch_hashkey IS NULL
     ),
-    -- Satellite (single-active): làm giàu thuộc tính, bản mới nhất đến :etl_date
     sat_latest AS (
         SELECT
             branch_hashkey,
@@ -1120,7 +1112,6 @@
         WHERE source_event_date &lt;= TO_DATE(:etl_date, 'yyyyMMdd')
         GROUP BY branch_hashkey
     ),
-    -- Satellite branch_mapping (single-active)
     bm_latest AS (
         SELECT
             branch_hashkey,
@@ -1131,18 +1122,23 @@
         WHERE source_event_date &lt;= TO_DATE(:etl_date, 'yyyyMMdd')
         GROUP BY branch_hashkey
     ),
+    area_map AS (
+        SELECT OU_ID, CB_AREA_ID, CB_AREA_NM
+        FROM ou_area_mapping
+        WHERE CB_AREA_ID IS NOT NULL
+    ),
     source_data AS (
         SELECT
-            h.branch_hashkey                                    AS OU_ID,
-            h.business_key                                      AS OU_CODE,
-            SUBSTRING_INDEX(si.t_company_name, '::', 1)         AS OU_NM,
-            prn_hub.branch_hashkey                              AS PRN_OU_ID,
-            SUBSTRING_INDEX(prn_si.t_company_name, '::', 1)     AS PRN_OU_NM,
-            bm.parent_branch_code                               AS PRN_OU_CODE,
+            h.branch_hashkey                                AS OU_ID,
+            h.business_key                                  AS OU_CODE,
+            SUBSTRING_INDEX(si.t_company_name, '::', 1)     AS OU_NM,
+            prn_hub.branch_hashkey                          AS PRN_OU_ID,
+            SUBSTRING_INDEX(prn_si.t_company_name, '::', 1) AS PRN_OU_NM,
+            bm.parent_branch_code                           AS PRN_OU_CODE,
             am.CB_AREA_ID,
             am.CB_AREA_NM,
-            bm.address                                          AS OU_ADR,
-            bm.phone_number                                     AS OU_PH,
+            bm.address                                      AS OU_ADR,
+            bm.phone_number                                 AS OU_PH,
             h.source_event_date
         FROM hub_active h
         LEFT JOIN sat_latest si
@@ -1153,15 +1149,10 @@
             ON prn_hub.business_key = bm.parent_branch_code
         LEFT JOIN sat_latest prn_si
             ON prn_hub.branch_hashkey = prn_si.branch_hashkey
-        LEFT JOIN ou_area_mapping am
+        LEFT JOIN area_map am
             ON am.OU_ID = h.business_key
         WHERE UPPER(COALESCE(si.t_company_name, '')) &lt;&gt; 'NOT USED'
           AND h.business_key &lt;&gt; 'VN0010001'
-    ),
-    -- Max OU_DIM_ID hiện tại
-    max_id AS (
-        SELECT COALESCE(MAX(OU_DIM_ID), 0) AS max_val
-        FROM CB_OU_DIM
     ),
     changed AS (
         SELECT src.OU_ID
@@ -1191,9 +1182,8 @@
             src.source_event_date,
             src.OU_ADR,
             src.OU_PH,
-            m.max_val + ROW_NUMBER() OVER (ORDER BY src.OU_ID)  AS NEW_OU_DIM_ID
+            uuid()                                              AS NEW_OU_DIM_ID
         FROM source_data src
-        CROSS JOIN max_id m
         LEFT JOIN CB_OU_DIM tgt_chk
             ON  src.OU_ID        = tgt_chk.OU_ID
             AND tgt_chk.EFF_TO_DT IS NULL
@@ -1202,8 +1192,8 @@
     ),
     close_records AS (
         SELECT
-            'CLOSE'                                             AS rec_type,
-            'D'                                                 AS CDC_FLAG,
+            'CLOSE'                AS rec_type,
+            'D'                    AS CDC_FLAG,
             tgt.OU_ID,
             tgt.OU_NM,
             tgt.OU_CODE,
@@ -1212,10 +1202,10 @@
             tgt.PRN_OU_CODE,
             tgt.CB_AREA_ID,
             tgt.CB_AREA_NM,
-            tgt.START_WK_DT                                     AS source_event_date,
+            tgt.START_WK_DT        AS source_event_date,
             tgt.OU_ADR,
             tgt.OU_PH,
-            tgt.OU_DIM_ID                                       AS NEW_OU_DIM_ID
+            tgt.OU_DIM_ID          AS NEW_OU_DIM_ID 
         FROM CB_OU_DIM tgt
         LEFT JOIN source_data src ON src.OU_ID = tgt.OU_ID
         WHERE tgt.EFF_TO_DT IS NULL
@@ -1224,9 +1214,25 @@
                 OR src.OU_ID IS NULL
               )
     )
-    SELECT * FROM new_records
+    SELECT
+        rec_type, CDC_FLAG,
+        OU_ID, OU_NM, OU_CODE,
+        PRN_OU_ID, PRN_OU_NM, PRN_OU_CODE,
+        CB_AREA_ID, CB_AREA_NM,
+        source_event_date,
+        OU_ADR, OU_PH,
+        NEW_OU_DIM_ID
+    FROM new_records
     UNION ALL
-    SELECT * FROM close_records
+    SELECT
+        rec_type, CDC_FLAG,
+        OU_ID, OU_NM, OU_CODE,
+        PRN_OU_ID, PRN_OU_NM, PRN_OU_CODE,
+        CB_AREA_ID, CB_AREA_NM,
+        source_event_date,
+        OU_ADR, OU_PH,
+        NEW_OU_DIM_ID
+    FROM close_records
 ) src
 ON  tgt.OU_ID     = src.OU_ID
 AND tgt.EFF_TO_DT IS NULL
@@ -1260,8 +1266,7 @@
 WHEN MATCHED AND src.rec_type = 'CLOSE' THEN
     UPDATE SET
         tgt.EFF_TO_DT = DATE_SUB(TO_DATE(:etl_date, 'yyyyMMdd'), 1),
-        tgt.CRT_TM    = CURRENT_TIMESTAMP()
-;</t>
+        tgt.CRT_TM    = CURRENT_TIMESTAMP()</t>
   </si>
   <si>
     <t>V_TB_AR_DTL_BDH
@@ -3617,7 +3622,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="145">
+  <cellXfs count="146">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3926,6 +3931,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -4371,544 +4379,544 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" ht="30" customHeight="1">
-      <c r="A1" s="113" t="s">
+      <c r="A1" s="114" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="113"/>
-      <c r="C1" s="113"/>
-      <c r="D1" s="113"/>
-      <c r="E1" s="113"/>
-      <c r="F1" s="113"/>
-      <c r="G1" s="113"/>
-      <c r="H1" s="113"/>
-      <c r="I1" s="113"/>
-      <c r="J1" s="113"/>
-      <c r="K1" s="113"/>
-      <c r="L1" s="113"/>
-      <c r="M1" s="113"/>
-      <c r="N1" s="113"/>
-      <c r="O1" s="113"/>
-      <c r="P1" s="113"/>
-      <c r="Q1" s="113"/>
-      <c r="R1" s="113"/>
-      <c r="S1" s="113"/>
-      <c r="T1" s="113"/>
-      <c r="U1" s="113"/>
+      <c r="B1" s="114"/>
+      <c r="C1" s="114"/>
+      <c r="D1" s="114"/>
+      <c r="E1" s="114"/>
+      <c r="F1" s="114"/>
+      <c r="G1" s="114"/>
+      <c r="H1" s="114"/>
+      <c r="I1" s="114"/>
+      <c r="J1" s="114"/>
+      <c r="K1" s="114"/>
+      <c r="L1" s="114"/>
+      <c r="M1" s="114"/>
+      <c r="N1" s="114"/>
+      <c r="O1" s="114"/>
+      <c r="P1" s="114"/>
+      <c r="Q1" s="114"/>
+      <c r="R1" s="114"/>
+      <c r="S1" s="114"/>
+      <c r="T1" s="114"/>
+      <c r="U1" s="114"/>
     </row>
     <row r="2" spans="1:21" ht="6" customHeight="1"/>
     <row r="3" spans="1:21" ht="22.15" customHeight="1">
-      <c r="B3" s="114" t="s">
+      <c r="B3" s="115" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="114"/>
-      <c r="D3" s="114"/>
-      <c r="E3" s="114"/>
-      <c r="G3" s="114" t="s">
+      <c r="C3" s="115"/>
+      <c r="D3" s="115"/>
+      <c r="E3" s="115"/>
+      <c r="G3" s="115" t="s">
         <v>2</v>
       </c>
-      <c r="H3" s="114"/>
-      <c r="I3" s="114"/>
-      <c r="J3" s="114"/>
-      <c r="L3" s="115" t="s">
+      <c r="H3" s="115"/>
+      <c r="I3" s="115"/>
+      <c r="J3" s="115"/>
+      <c r="L3" s="116" t="s">
         <v>3</v>
       </c>
-      <c r="M3" s="115"/>
-      <c r="N3" s="115"/>
-      <c r="O3" s="115"/>
-      <c r="Q3" s="116" t="s">
+      <c r="M3" s="116"/>
+      <c r="N3" s="116"/>
+      <c r="O3" s="116"/>
+      <c r="Q3" s="117" t="s">
         <v>4</v>
       </c>
-      <c r="R3" s="116"/>
-      <c r="S3" s="116"/>
-      <c r="T3" s="116"/>
+      <c r="R3" s="117"/>
+      <c r="S3" s="117"/>
+      <c r="T3" s="117"/>
     </row>
     <row r="4" spans="1:21" ht="19.899999999999999" customHeight="1">
-      <c r="B4" s="117" t="s">
+      <c r="B4" s="118" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="117"/>
-      <c r="D4" s="117"/>
-      <c r="E4" s="117"/>
-      <c r="G4" s="117" t="s">
+      <c r="C4" s="118"/>
+      <c r="D4" s="118"/>
+      <c r="E4" s="118"/>
+      <c r="G4" s="118" t="s">
         <v>6</v>
       </c>
-      <c r="H4" s="117"/>
-      <c r="I4" s="117"/>
-      <c r="J4" s="117"/>
-      <c r="L4" s="118" t="s">
-        <v>7</v>
-      </c>
-      <c r="M4" s="118"/>
-      <c r="N4" s="118"/>
-      <c r="O4" s="118"/>
-      <c r="Q4" s="119" t="s">
+      <c r="H4" s="118"/>
+      <c r="I4" s="118"/>
+      <c r="J4" s="118"/>
+      <c r="L4" s="119" t="s">
+        <v>7</v>
+      </c>
+      <c r="M4" s="119"/>
+      <c r="N4" s="119"/>
+      <c r="O4" s="119"/>
+      <c r="Q4" s="120" t="s">
         <v>8</v>
       </c>
-      <c r="R4" s="119"/>
-      <c r="S4" s="119"/>
-      <c r="T4" s="119"/>
+      <c r="R4" s="120"/>
+      <c r="S4" s="120"/>
+      <c r="T4" s="120"/>
     </row>
     <row r="5" spans="1:21" ht="19.899999999999999" customHeight="1">
-      <c r="B5" s="117"/>
-      <c r="C5" s="117"/>
-      <c r="D5" s="117"/>
-      <c r="E5" s="117"/>
-      <c r="G5" s="117"/>
-      <c r="H5" s="117"/>
-      <c r="I5" s="117"/>
-      <c r="J5" s="117"/>
-      <c r="L5" s="118"/>
-      <c r="M5" s="118"/>
-      <c r="N5" s="118"/>
-      <c r="O5" s="118"/>
+      <c r="B5" s="118"/>
+      <c r="C5" s="118"/>
+      <c r="D5" s="118"/>
+      <c r="E5" s="118"/>
+      <c r="G5" s="118"/>
+      <c r="H5" s="118"/>
+      <c r="I5" s="118"/>
+      <c r="J5" s="118"/>
+      <c r="L5" s="119"/>
+      <c r="M5" s="119"/>
+      <c r="N5" s="119"/>
+      <c r="O5" s="119"/>
       <c r="P5" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="Q5" s="119"/>
-      <c r="R5" s="119"/>
-      <c r="S5" s="119"/>
-      <c r="T5" s="119"/>
+      <c r="Q5" s="120"/>
+      <c r="R5" s="120"/>
+      <c r="S5" s="120"/>
+      <c r="T5" s="120"/>
     </row>
     <row r="6" spans="1:21" ht="19.899999999999999" customHeight="1">
-      <c r="B6" s="117"/>
-      <c r="C6" s="117"/>
-      <c r="D6" s="117"/>
-      <c r="E6" s="117"/>
-      <c r="G6" s="117"/>
-      <c r="H6" s="117"/>
-      <c r="I6" s="117"/>
-      <c r="J6" s="117"/>
-      <c r="L6" s="118"/>
-      <c r="M6" s="118"/>
-      <c r="N6" s="118"/>
-      <c r="O6" s="118"/>
-      <c r="Q6" s="119"/>
-      <c r="R6" s="119"/>
-      <c r="S6" s="119"/>
-      <c r="T6" s="119"/>
+      <c r="B6" s="118"/>
+      <c r="C6" s="118"/>
+      <c r="D6" s="118"/>
+      <c r="E6" s="118"/>
+      <c r="G6" s="118"/>
+      <c r="H6" s="118"/>
+      <c r="I6" s="118"/>
+      <c r="J6" s="118"/>
+      <c r="L6" s="119"/>
+      <c r="M6" s="119"/>
+      <c r="N6" s="119"/>
+      <c r="O6" s="119"/>
+      <c r="Q6" s="120"/>
+      <c r="R6" s="120"/>
+      <c r="S6" s="120"/>
+      <c r="T6" s="120"/>
     </row>
     <row r="7" spans="1:21" ht="7.15" customHeight="1">
-      <c r="B7" s="117"/>
-      <c r="C7" s="117"/>
-      <c r="D7" s="117"/>
-      <c r="E7" s="117"/>
-      <c r="G7" s="117"/>
-      <c r="H7" s="117"/>
-      <c r="I7" s="117"/>
-      <c r="J7" s="117"/>
-      <c r="L7" s="118"/>
-      <c r="M7" s="118"/>
-      <c r="N7" s="118"/>
-      <c r="O7" s="118"/>
+      <c r="B7" s="118"/>
+      <c r="C7" s="118"/>
+      <c r="D7" s="118"/>
+      <c r="E7" s="118"/>
+      <c r="G7" s="118"/>
+      <c r="H7" s="118"/>
+      <c r="I7" s="118"/>
+      <c r="J7" s="118"/>
+      <c r="L7" s="119"/>
+      <c r="M7" s="119"/>
+      <c r="N7" s="119"/>
+      <c r="O7" s="119"/>
     </row>
     <row r="8" spans="1:21" ht="19.899999999999999" customHeight="1">
-      <c r="B8" s="117"/>
-      <c r="C8" s="117"/>
-      <c r="D8" s="117"/>
-      <c r="E8" s="117"/>
-      <c r="G8" s="117"/>
-      <c r="H8" s="117"/>
-      <c r="I8" s="117"/>
-      <c r="J8" s="117"/>
-      <c r="L8" s="118"/>
-      <c r="M8" s="118"/>
-      <c r="N8" s="118"/>
-      <c r="O8" s="118"/>
-      <c r="Q8" s="120" t="s">
+      <c r="B8" s="118"/>
+      <c r="C8" s="118"/>
+      <c r="D8" s="118"/>
+      <c r="E8" s="118"/>
+      <c r="G8" s="118"/>
+      <c r="H8" s="118"/>
+      <c r="I8" s="118"/>
+      <c r="J8" s="118"/>
+      <c r="L8" s="119"/>
+      <c r="M8" s="119"/>
+      <c r="N8" s="119"/>
+      <c r="O8" s="119"/>
+      <c r="Q8" s="121" t="s">
         <v>10</v>
       </c>
-      <c r="R8" s="120"/>
-      <c r="S8" s="120"/>
-      <c r="T8" s="120"/>
+      <c r="R8" s="121"/>
+      <c r="S8" s="121"/>
+      <c r="T8" s="121"/>
     </row>
     <row r="9" spans="1:21" ht="19.899999999999999" customHeight="1">
-      <c r="B9" s="117"/>
-      <c r="C9" s="117"/>
-      <c r="D9" s="117"/>
-      <c r="E9" s="117"/>
-      <c r="G9" s="117"/>
-      <c r="H9" s="117"/>
-      <c r="I9" s="117"/>
-      <c r="J9" s="117"/>
-      <c r="L9" s="118"/>
-      <c r="M9" s="118"/>
-      <c r="N9" s="118"/>
-      <c r="O9" s="118"/>
+      <c r="B9" s="118"/>
+      <c r="C9" s="118"/>
+      <c r="D9" s="118"/>
+      <c r="E9" s="118"/>
+      <c r="G9" s="118"/>
+      <c r="H9" s="118"/>
+      <c r="I9" s="118"/>
+      <c r="J9" s="118"/>
+      <c r="L9" s="119"/>
+      <c r="M9" s="119"/>
+      <c r="N9" s="119"/>
+      <c r="O9" s="119"/>
       <c r="P9" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="Q9" s="120"/>
-      <c r="R9" s="120"/>
-      <c r="S9" s="120"/>
-      <c r="T9" s="120"/>
+      <c r="Q9" s="121"/>
+      <c r="R9" s="121"/>
+      <c r="S9" s="121"/>
+      <c r="T9" s="121"/>
     </row>
     <row r="10" spans="1:21" ht="19.899999999999999" customHeight="1">
-      <c r="B10" s="117"/>
-      <c r="C10" s="117"/>
-      <c r="D10" s="117"/>
-      <c r="E10" s="117"/>
-      <c r="G10" s="117"/>
-      <c r="H10" s="117"/>
-      <c r="I10" s="117"/>
-      <c r="J10" s="117"/>
-      <c r="L10" s="118"/>
-      <c r="M10" s="118"/>
-      <c r="N10" s="118"/>
-      <c r="O10" s="118"/>
-      <c r="Q10" s="120"/>
-      <c r="R10" s="120"/>
-      <c r="S10" s="120"/>
-      <c r="T10" s="120"/>
+      <c r="B10" s="118"/>
+      <c r="C10" s="118"/>
+      <c r="D10" s="118"/>
+      <c r="E10" s="118"/>
+      <c r="G10" s="118"/>
+      <c r="H10" s="118"/>
+      <c r="I10" s="118"/>
+      <c r="J10" s="118"/>
+      <c r="L10" s="119"/>
+      <c r="M10" s="119"/>
+      <c r="N10" s="119"/>
+      <c r="O10" s="119"/>
+      <c r="Q10" s="121"/>
+      <c r="R10" s="121"/>
+      <c r="S10" s="121"/>
+      <c r="T10" s="121"/>
     </row>
     <row r="11" spans="1:21" ht="7.15" customHeight="1">
-      <c r="B11" s="117"/>
-      <c r="C11" s="117"/>
-      <c r="D11" s="117"/>
-      <c r="E11" s="117"/>
-      <c r="G11" s="117"/>
-      <c r="H11" s="117"/>
-      <c r="I11" s="117"/>
-      <c r="J11" s="117"/>
-      <c r="L11" s="118"/>
-      <c r="M11" s="118"/>
-      <c r="N11" s="118"/>
-      <c r="O11" s="118"/>
+      <c r="B11" s="118"/>
+      <c r="C11" s="118"/>
+      <c r="D11" s="118"/>
+      <c r="E11" s="118"/>
+      <c r="G11" s="118"/>
+      <c r="H11" s="118"/>
+      <c r="I11" s="118"/>
+      <c r="J11" s="118"/>
+      <c r="L11" s="119"/>
+      <c r="M11" s="119"/>
+      <c r="N11" s="119"/>
+      <c r="O11" s="119"/>
     </row>
     <row r="12" spans="1:21" ht="19.899999999999999" customHeight="1">
-      <c r="B12" s="117"/>
-      <c r="C12" s="117"/>
-      <c r="D12" s="117"/>
-      <c r="E12" s="117"/>
-      <c r="G12" s="117"/>
-      <c r="H12" s="117"/>
-      <c r="I12" s="117"/>
-      <c r="J12" s="117"/>
-      <c r="L12" s="118"/>
-      <c r="M12" s="118"/>
-      <c r="N12" s="118"/>
-      <c r="O12" s="118"/>
-      <c r="Q12" s="120" t="s">
+      <c r="B12" s="118"/>
+      <c r="C12" s="118"/>
+      <c r="D12" s="118"/>
+      <c r="E12" s="118"/>
+      <c r="G12" s="118"/>
+      <c r="H12" s="118"/>
+      <c r="I12" s="118"/>
+      <c r="J12" s="118"/>
+      <c r="L12" s="119"/>
+      <c r="M12" s="119"/>
+      <c r="N12" s="119"/>
+      <c r="O12" s="119"/>
+      <c r="Q12" s="121" t="s">
         <v>11</v>
       </c>
-      <c r="R12" s="120"/>
-      <c r="S12" s="120"/>
-      <c r="T12" s="120"/>
+      <c r="R12" s="121"/>
+      <c r="S12" s="121"/>
+      <c r="T12" s="121"/>
     </row>
     <row r="13" spans="1:21" ht="19.899999999999999" customHeight="1">
-      <c r="B13" s="117"/>
-      <c r="C13" s="117"/>
-      <c r="D13" s="117"/>
-      <c r="E13" s="117"/>
+      <c r="B13" s="118"/>
+      <c r="C13" s="118"/>
+      <c r="D13" s="118"/>
+      <c r="E13" s="118"/>
       <c r="F13" s="2"/>
-      <c r="G13" s="117"/>
-      <c r="H13" s="117"/>
-      <c r="I13" s="117"/>
-      <c r="J13" s="117"/>
+      <c r="G13" s="118"/>
+      <c r="H13" s="118"/>
+      <c r="I13" s="118"/>
+      <c r="J13" s="118"/>
       <c r="K13" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="L13" s="118"/>
-      <c r="M13" s="118"/>
-      <c r="N13" s="118"/>
-      <c r="O13" s="118"/>
+      <c r="L13" s="119"/>
+      <c r="M13" s="119"/>
+      <c r="N13" s="119"/>
+      <c r="O13" s="119"/>
       <c r="P13" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="Q13" s="120"/>
-      <c r="R13" s="120"/>
-      <c r="S13" s="120"/>
-      <c r="T13" s="120"/>
+      <c r="Q13" s="121"/>
+      <c r="R13" s="121"/>
+      <c r="S13" s="121"/>
+      <c r="T13" s="121"/>
     </row>
     <row r="14" spans="1:21" ht="19.899999999999999" customHeight="1">
-      <c r="B14" s="117"/>
-      <c r="C14" s="117"/>
-      <c r="D14" s="117"/>
-      <c r="E14" s="117"/>
-      <c r="G14" s="117"/>
-      <c r="H14" s="117"/>
-      <c r="I14" s="117"/>
-      <c r="J14" s="117"/>
-      <c r="L14" s="118"/>
-      <c r="M14" s="118"/>
-      <c r="N14" s="118"/>
-      <c r="O14" s="118"/>
-      <c r="Q14" s="120"/>
-      <c r="R14" s="120"/>
-      <c r="S14" s="120"/>
-      <c r="T14" s="120"/>
+      <c r="B14" s="118"/>
+      <c r="C14" s="118"/>
+      <c r="D14" s="118"/>
+      <c r="E14" s="118"/>
+      <c r="G14" s="118"/>
+      <c r="H14" s="118"/>
+      <c r="I14" s="118"/>
+      <c r="J14" s="118"/>
+      <c r="L14" s="119"/>
+      <c r="M14" s="119"/>
+      <c r="N14" s="119"/>
+      <c r="O14" s="119"/>
+      <c r="Q14" s="121"/>
+      <c r="R14" s="121"/>
+      <c r="S14" s="121"/>
+      <c r="T14" s="121"/>
     </row>
     <row r="15" spans="1:21" ht="7.15" customHeight="1">
-      <c r="B15" s="117"/>
-      <c r="C15" s="117"/>
-      <c r="D15" s="117"/>
-      <c r="E15" s="117"/>
-      <c r="G15" s="117"/>
-      <c r="H15" s="117"/>
-      <c r="I15" s="117"/>
-      <c r="J15" s="117"/>
-      <c r="L15" s="118"/>
-      <c r="M15" s="118"/>
-      <c r="N15" s="118"/>
-      <c r="O15" s="118"/>
+      <c r="B15" s="118"/>
+      <c r="C15" s="118"/>
+      <c r="D15" s="118"/>
+      <c r="E15" s="118"/>
+      <c r="G15" s="118"/>
+      <c r="H15" s="118"/>
+      <c r="I15" s="118"/>
+      <c r="J15" s="118"/>
+      <c r="L15" s="119"/>
+      <c r="M15" s="119"/>
+      <c r="N15" s="119"/>
+      <c r="O15" s="119"/>
     </row>
     <row r="16" spans="1:21" ht="19.899999999999999" customHeight="1">
-      <c r="B16" s="117"/>
-      <c r="C16" s="117"/>
-      <c r="D16" s="117"/>
-      <c r="E16" s="117"/>
-      <c r="G16" s="117"/>
-      <c r="H16" s="117"/>
-      <c r="I16" s="117"/>
-      <c r="J16" s="117"/>
-      <c r="L16" s="118"/>
-      <c r="M16" s="118"/>
-      <c r="N16" s="118"/>
-      <c r="O16" s="118"/>
-      <c r="Q16" s="119" t="s">
+      <c r="B16" s="118"/>
+      <c r="C16" s="118"/>
+      <c r="D16" s="118"/>
+      <c r="E16" s="118"/>
+      <c r="G16" s="118"/>
+      <c r="H16" s="118"/>
+      <c r="I16" s="118"/>
+      <c r="J16" s="118"/>
+      <c r="L16" s="119"/>
+      <c r="M16" s="119"/>
+      <c r="N16" s="119"/>
+      <c r="O16" s="119"/>
+      <c r="Q16" s="120" t="s">
         <v>12</v>
       </c>
-      <c r="R16" s="119"/>
-      <c r="S16" s="119"/>
-      <c r="T16" s="119"/>
+      <c r="R16" s="120"/>
+      <c r="S16" s="120"/>
+      <c r="T16" s="120"/>
     </row>
     <row r="17" spans="2:20" ht="19.899999999999999" customHeight="1">
-      <c r="B17" s="117"/>
-      <c r="C17" s="117"/>
-      <c r="D17" s="117"/>
-      <c r="E17" s="117"/>
+      <c r="B17" s="118"/>
+      <c r="C17" s="118"/>
+      <c r="D17" s="118"/>
+      <c r="E17" s="118"/>
       <c r="F17" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="G17" s="117"/>
-      <c r="H17" s="117"/>
-      <c r="I17" s="117"/>
-      <c r="J17" s="117"/>
-      <c r="L17" s="118"/>
-      <c r="M17" s="118"/>
-      <c r="N17" s="118"/>
-      <c r="O17" s="118"/>
+      <c r="G17" s="118"/>
+      <c r="H17" s="118"/>
+      <c r="I17" s="118"/>
+      <c r="J17" s="118"/>
+      <c r="L17" s="119"/>
+      <c r="M17" s="119"/>
+      <c r="N17" s="119"/>
+      <c r="O17" s="119"/>
       <c r="P17" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="Q17" s="119"/>
-      <c r="R17" s="119"/>
-      <c r="S17" s="119"/>
-      <c r="T17" s="119"/>
+      <c r="Q17" s="120"/>
+      <c r="R17" s="120"/>
+      <c r="S17" s="120"/>
+      <c r="T17" s="120"/>
     </row>
     <row r="18" spans="2:20" ht="19.899999999999999" customHeight="1">
-      <c r="B18" s="117"/>
-      <c r="C18" s="117"/>
-      <c r="D18" s="117"/>
-      <c r="E18" s="117"/>
-      <c r="G18" s="117"/>
-      <c r="H18" s="117"/>
-      <c r="I18" s="117"/>
-      <c r="J18" s="117"/>
-      <c r="L18" s="118"/>
-      <c r="M18" s="118"/>
-      <c r="N18" s="118"/>
-      <c r="O18" s="118"/>
-      <c r="Q18" s="119"/>
-      <c r="R18" s="119"/>
-      <c r="S18" s="119"/>
-      <c r="T18" s="119"/>
+      <c r="B18" s="118"/>
+      <c r="C18" s="118"/>
+      <c r="D18" s="118"/>
+      <c r="E18" s="118"/>
+      <c r="G18" s="118"/>
+      <c r="H18" s="118"/>
+      <c r="I18" s="118"/>
+      <c r="J18" s="118"/>
+      <c r="L18" s="119"/>
+      <c r="M18" s="119"/>
+      <c r="N18" s="119"/>
+      <c r="O18" s="119"/>
+      <c r="Q18" s="120"/>
+      <c r="R18" s="120"/>
+      <c r="S18" s="120"/>
+      <c r="T18" s="120"/>
     </row>
     <row r="19" spans="2:20" ht="10.15" customHeight="1">
-      <c r="B19" s="117"/>
-      <c r="C19" s="117"/>
-      <c r="D19" s="117"/>
-      <c r="E19" s="117"/>
-      <c r="G19" s="117"/>
-      <c r="H19" s="117"/>
-      <c r="I19" s="117"/>
-      <c r="J19" s="117"/>
-      <c r="L19" s="118"/>
-      <c r="M19" s="118"/>
-      <c r="N19" s="118"/>
-      <c r="O19" s="118"/>
+      <c r="B19" s="118"/>
+      <c r="C19" s="118"/>
+      <c r="D19" s="118"/>
+      <c r="E19" s="118"/>
+      <c r="G19" s="118"/>
+      <c r="H19" s="118"/>
+      <c r="I19" s="118"/>
+      <c r="J19" s="118"/>
+      <c r="L19" s="119"/>
+      <c r="M19" s="119"/>
+      <c r="N19" s="119"/>
+      <c r="O19" s="119"/>
     </row>
     <row r="20" spans="2:20" ht="19.899999999999999" customHeight="1">
-      <c r="B20" s="117"/>
-      <c r="C20" s="117"/>
-      <c r="D20" s="117"/>
-      <c r="E20" s="117"/>
-      <c r="G20" s="117"/>
-      <c r="H20" s="117"/>
-      <c r="I20" s="117"/>
-      <c r="J20" s="117"/>
-      <c r="L20" s="118"/>
-      <c r="M20" s="118"/>
-      <c r="N20" s="118"/>
-      <c r="O20" s="118"/>
-      <c r="Q20" s="120" t="s">
+      <c r="B20" s="118"/>
+      <c r="C20" s="118"/>
+      <c r="D20" s="118"/>
+      <c r="E20" s="118"/>
+      <c r="G20" s="118"/>
+      <c r="H20" s="118"/>
+      <c r="I20" s="118"/>
+      <c r="J20" s="118"/>
+      <c r="L20" s="119"/>
+      <c r="M20" s="119"/>
+      <c r="N20" s="119"/>
+      <c r="O20" s="119"/>
+      <c r="Q20" s="121" t="s">
         <v>13</v>
       </c>
-      <c r="R20" s="120"/>
-      <c r="S20" s="120"/>
-      <c r="T20" s="120"/>
+      <c r="R20" s="121"/>
+      <c r="S20" s="121"/>
+      <c r="T20" s="121"/>
     </row>
     <row r="21" spans="2:20" ht="19.899999999999999" customHeight="1">
-      <c r="B21" s="117"/>
-      <c r="C21" s="117"/>
-      <c r="D21" s="117"/>
-      <c r="E21" s="117"/>
-      <c r="G21" s="117"/>
-      <c r="H21" s="117"/>
-      <c r="I21" s="117"/>
-      <c r="J21" s="117"/>
-      <c r="L21" s="118"/>
-      <c r="M21" s="118"/>
-      <c r="N21" s="118"/>
-      <c r="O21" s="118"/>
+      <c r="B21" s="118"/>
+      <c r="C21" s="118"/>
+      <c r="D21" s="118"/>
+      <c r="E21" s="118"/>
+      <c r="G21" s="118"/>
+      <c r="H21" s="118"/>
+      <c r="I21" s="118"/>
+      <c r="J21" s="118"/>
+      <c r="L21" s="119"/>
+      <c r="M21" s="119"/>
+      <c r="N21" s="119"/>
+      <c r="O21" s="119"/>
       <c r="P21" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="Q21" s="120"/>
-      <c r="R21" s="120"/>
-      <c r="S21" s="120"/>
-      <c r="T21" s="120"/>
+      <c r="Q21" s="121"/>
+      <c r="R21" s="121"/>
+      <c r="S21" s="121"/>
+      <c r="T21" s="121"/>
     </row>
     <row r="22" spans="2:20" ht="19.899999999999999" customHeight="1">
-      <c r="B22" s="117"/>
-      <c r="C22" s="117"/>
-      <c r="D22" s="117"/>
-      <c r="E22" s="117"/>
-      <c r="G22" s="117"/>
-      <c r="H22" s="117"/>
-      <c r="I22" s="117"/>
-      <c r="J22" s="117"/>
-      <c r="L22" s="118"/>
-      <c r="M22" s="118"/>
-      <c r="N22" s="118"/>
-      <c r="O22" s="118"/>
-      <c r="Q22" s="120"/>
-      <c r="R22" s="120"/>
-      <c r="S22" s="120"/>
-      <c r="T22" s="120"/>
+      <c r="B22" s="118"/>
+      <c r="C22" s="118"/>
+      <c r="D22" s="118"/>
+      <c r="E22" s="118"/>
+      <c r="G22" s="118"/>
+      <c r="H22" s="118"/>
+      <c r="I22" s="118"/>
+      <c r="J22" s="118"/>
+      <c r="L22" s="119"/>
+      <c r="M22" s="119"/>
+      <c r="N22" s="119"/>
+      <c r="O22" s="119"/>
+      <c r="Q22" s="121"/>
+      <c r="R22" s="121"/>
+      <c r="S22" s="121"/>
+      <c r="T22" s="121"/>
     </row>
     <row r="23" spans="2:20" ht="7.9" customHeight="1">
-      <c r="B23" s="117"/>
-      <c r="C23" s="117"/>
-      <c r="D23" s="117"/>
-      <c r="E23" s="117"/>
-      <c r="G23" s="117"/>
-      <c r="H23" s="117"/>
-      <c r="I23" s="117"/>
-      <c r="J23" s="117"/>
+      <c r="B23" s="118"/>
+      <c r="C23" s="118"/>
+      <c r="D23" s="118"/>
+      <c r="E23" s="118"/>
+      <c r="G23" s="118"/>
+      <c r="H23" s="118"/>
+      <c r="I23" s="118"/>
+      <c r="J23" s="118"/>
     </row>
     <row r="24" spans="2:20" ht="19.899999999999999" customHeight="1">
-      <c r="B24" s="117"/>
-      <c r="C24" s="117"/>
-      <c r="D24" s="117"/>
-      <c r="E24" s="117"/>
-      <c r="G24" s="117"/>
-      <c r="H24" s="117"/>
-      <c r="I24" s="117"/>
-      <c r="J24" s="117"/>
-      <c r="L24" s="119" t="s">
+      <c r="B24" s="118"/>
+      <c r="C24" s="118"/>
+      <c r="D24" s="118"/>
+      <c r="E24" s="118"/>
+      <c r="G24" s="118"/>
+      <c r="H24" s="118"/>
+      <c r="I24" s="118"/>
+      <c r="J24" s="118"/>
+      <c r="L24" s="120" t="s">
         <v>14</v>
       </c>
-      <c r="M24" s="119"/>
-      <c r="N24" s="119"/>
-      <c r="O24" s="119"/>
-      <c r="P24" s="121" t="s">
+      <c r="M24" s="120"/>
+      <c r="N24" s="120"/>
+      <c r="O24" s="120"/>
+      <c r="P24" s="122" t="s">
         <v>9</v>
       </c>
-      <c r="Q24" s="124" t="s">
+      <c r="Q24" s="125" t="s">
         <v>15</v>
       </c>
-      <c r="R24" s="125"/>
+      <c r="R24" s="126"/>
     </row>
     <row r="25" spans="2:20" ht="19.899999999999999" customHeight="1">
-      <c r="B25" s="117"/>
-      <c r="C25" s="117"/>
-      <c r="D25" s="117"/>
-      <c r="E25" s="117"/>
+      <c r="B25" s="118"/>
+      <c r="C25" s="118"/>
+      <c r="D25" s="118"/>
+      <c r="E25" s="118"/>
       <c r="F25" s="2"/>
-      <c r="G25" s="117"/>
-      <c r="H25" s="117"/>
-      <c r="I25" s="117"/>
-      <c r="J25" s="117"/>
+      <c r="G25" s="118"/>
+      <c r="H25" s="118"/>
+      <c r="I25" s="118"/>
+      <c r="J25" s="118"/>
       <c r="K25" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="L25" s="119"/>
-      <c r="M25" s="119"/>
-      <c r="N25" s="119"/>
-      <c r="O25" s="119"/>
-      <c r="P25" s="122"/>
-      <c r="Q25" s="126"/>
-      <c r="R25" s="127"/>
+      <c r="L25" s="120"/>
+      <c r="M25" s="120"/>
+      <c r="N25" s="120"/>
+      <c r="O25" s="120"/>
+      <c r="P25" s="123"/>
+      <c r="Q25" s="127"/>
+      <c r="R25" s="128"/>
     </row>
     <row r="26" spans="2:20" ht="19.899999999999999" customHeight="1">
-      <c r="B26" s="117"/>
-      <c r="C26" s="117"/>
-      <c r="D26" s="117"/>
-      <c r="E26" s="117"/>
-      <c r="G26" s="117"/>
-      <c r="H26" s="117"/>
-      <c r="I26" s="117"/>
-      <c r="J26" s="117"/>
-      <c r="L26" s="119"/>
-      <c r="M26" s="119"/>
-      <c r="N26" s="119"/>
-      <c r="O26" s="119"/>
-      <c r="P26" s="123"/>
-      <c r="Q26" s="126"/>
-      <c r="R26" s="127"/>
+      <c r="B26" s="118"/>
+      <c r="C26" s="118"/>
+      <c r="D26" s="118"/>
+      <c r="E26" s="118"/>
+      <c r="G26" s="118"/>
+      <c r="H26" s="118"/>
+      <c r="I26" s="118"/>
+      <c r="J26" s="118"/>
+      <c r="L26" s="120"/>
+      <c r="M26" s="120"/>
+      <c r="N26" s="120"/>
+      <c r="O26" s="120"/>
+      <c r="P26" s="124"/>
+      <c r="Q26" s="127"/>
+      <c r="R26" s="128"/>
     </row>
     <row r="27" spans="2:20" ht="15" customHeight="1">
-      <c r="B27" s="117"/>
-      <c r="C27" s="117"/>
-      <c r="D27" s="117"/>
-      <c r="E27" s="117"/>
-      <c r="G27" s="117"/>
-      <c r="H27" s="117"/>
-      <c r="I27" s="117"/>
-      <c r="J27" s="117"/>
-      <c r="Q27" s="126"/>
-      <c r="R27" s="127"/>
+      <c r="B27" s="118"/>
+      <c r="C27" s="118"/>
+      <c r="D27" s="118"/>
+      <c r="E27" s="118"/>
+      <c r="G27" s="118"/>
+      <c r="H27" s="118"/>
+      <c r="I27" s="118"/>
+      <c r="J27" s="118"/>
+      <c r="Q27" s="127"/>
+      <c r="R27" s="128"/>
     </row>
     <row r="28" spans="2:20" ht="22.15" customHeight="1">
-      <c r="B28" s="117"/>
-      <c r="C28" s="117"/>
-      <c r="D28" s="117"/>
-      <c r="E28" s="117"/>
+      <c r="B28" s="118"/>
+      <c r="C28" s="118"/>
+      <c r="D28" s="118"/>
+      <c r="E28" s="118"/>
       <c r="F28" s="2"/>
-      <c r="G28" s="117"/>
-      <c r="H28" s="117"/>
-      <c r="I28" s="117"/>
-      <c r="J28" s="117"/>
+      <c r="G28" s="118"/>
+      <c r="H28" s="118"/>
+      <c r="I28" s="118"/>
+      <c r="J28" s="118"/>
       <c r="K28" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="L28" s="119" t="s">
+      <c r="L28" s="120" t="s">
         <v>16</v>
       </c>
-      <c r="M28" s="119"/>
-      <c r="N28" s="119"/>
-      <c r="O28" s="119"/>
+      <c r="M28" s="120"/>
+      <c r="N28" s="120"/>
+      <c r="O28" s="120"/>
       <c r="P28" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="Q28" s="126"/>
-      <c r="R28" s="127"/>
+      <c r="Q28" s="127"/>
+      <c r="R28" s="128"/>
     </row>
     <row r="29" spans="2:20" ht="22.15" customHeight="1">
-      <c r="B29" s="117"/>
-      <c r="C29" s="117"/>
-      <c r="D29" s="117"/>
-      <c r="E29" s="117"/>
-      <c r="G29" s="117"/>
-      <c r="H29" s="117"/>
-      <c r="I29" s="117"/>
-      <c r="J29" s="117"/>
-      <c r="L29" s="119"/>
-      <c r="M29" s="119"/>
-      <c r="N29" s="119"/>
-      <c r="O29" s="119"/>
-      <c r="Q29" s="128"/>
-      <c r="R29" s="129"/>
+      <c r="B29" s="118"/>
+      <c r="C29" s="118"/>
+      <c r="D29" s="118"/>
+      <c r="E29" s="118"/>
+      <c r="G29" s="118"/>
+      <c r="H29" s="118"/>
+      <c r="I29" s="118"/>
+      <c r="J29" s="118"/>
+      <c r="L29" s="120"/>
+      <c r="M29" s="120"/>
+      <c r="N29" s="120"/>
+      <c r="O29" s="120"/>
+      <c r="Q29" s="129"/>
+      <c r="R29" s="130"/>
     </row>
     <row r="30" spans="2:20" ht="18" customHeight="1"/>
     <row r="31" spans="2:20" ht="18" customHeight="1"/>
@@ -4921,31 +4929,31 @@
     </row>
     <row r="34" spans="7:8" ht="29.25" customHeight="1">
       <c r="G34" s="5"/>
-      <c r="H34" s="142" t="s">
+      <c r="H34" s="143" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="35" spans="7:8" ht="23.25" customHeight="1">
       <c r="G35" s="6"/>
-      <c r="H35" s="142" t="s">
+      <c r="H35" s="143" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="36" spans="7:8" ht="25.5" customHeight="1">
       <c r="G36" s="7"/>
-      <c r="H36" s="142" t="s">
+      <c r="H36" s="143" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="37" spans="7:8" ht="25.15" customHeight="1">
       <c r="G37" s="8"/>
-      <c r="H37" s="142" t="s">
+      <c r="H37" s="143" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="38" spans="7:8" ht="25.15" customHeight="1">
       <c r="G38" s="9"/>
-      <c r="H38" s="142" t="s">
+      <c r="H38" s="143" t="s">
         <v>22</v>
       </c>
     </row>
@@ -5067,7 +5075,7 @@
       <c r="B8" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="24" t="s">
+      <c r="C8" s="113" t="s">
         <v>35</v>
       </c>
     </row>
@@ -5078,7 +5086,7 @@
       <c r="B9" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="141" t="s">
+      <c r="C9" s="24" t="s">
         <v>36</v>
       </c>
     </row>
@@ -5089,7 +5097,7 @@
       <c r="B10" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="24" t="s">
+      <c r="C10" s="142" t="s">
         <v>37</v>
       </c>
     </row>
@@ -5100,7 +5108,7 @@
       <c r="B11" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="24" t="s">
+      <c r="C11" s="142" t="s">
         <v>38</v>
       </c>
     </row>
@@ -5111,7 +5119,7 @@
       <c r="B12" t="s">
         <v>12</v>
       </c>
-      <c r="C12" s="24" t="s">
+      <c r="C12" s="142" t="s">
         <v>39</v>
       </c>
     </row>
@@ -5145,13 +5153,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="48" customHeight="1">
-      <c r="A1" s="130" t="s">
+      <c r="A1" s="131" t="s">
         <v>41</v>
       </c>
-      <c r="B1" s="143"/>
-      <c r="C1" s="143"/>
-      <c r="D1" s="143"/>
-      <c r="E1" s="143"/>
+      <c r="B1" s="144"/>
+      <c r="C1" s="144"/>
+      <c r="D1" s="144"/>
+      <c r="E1" s="144"/>
     </row>
     <row r="2" spans="1:5" ht="19.899999999999999" customHeight="1">
       <c r="A2" s="12" t="s">
@@ -5210,13 +5218,13 @@
       <c r="E5" s="17"/>
     </row>
     <row r="6" spans="1:5" ht="24" customHeight="1">
-      <c r="A6" s="131" t="s">
+      <c r="A6" s="132" t="s">
         <v>53</v>
       </c>
-      <c r="B6" s="144"/>
-      <c r="C6" s="144"/>
-      <c r="D6" s="144"/>
-      <c r="E6" s="144"/>
+      <c r="B6" s="145"/>
+      <c r="C6" s="145"/>
+      <c r="D6" s="145"/>
+      <c r="E6" s="145"/>
     </row>
     <row r="7" spans="1:5" ht="37.5" customHeight="1">
       <c r="A7" s="18" t="s">
@@ -6473,13 +6481,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="41.25" customHeight="1">
-      <c r="A1" s="130" t="s">
+      <c r="A1" s="131" t="s">
         <v>223</v>
       </c>
-      <c r="B1" s="143"/>
-      <c r="C1" s="143"/>
-      <c r="D1" s="143"/>
-      <c r="E1" s="143"/>
+      <c r="B1" s="144"/>
+      <c r="C1" s="144"/>
+      <c r="D1" s="144"/>
+      <c r="E1" s="144"/>
     </row>
     <row r="2" spans="1:5" ht="19.899999999999999" customHeight="1">
       <c r="A2" s="12" t="s">
@@ -6538,13 +6546,13 @@
       <c r="E5" s="17"/>
     </row>
     <row r="6" spans="1:5" ht="31.5" customHeight="1">
-      <c r="A6" s="131" t="s">
+      <c r="A6" s="132" t="s">
         <v>53</v>
       </c>
-      <c r="B6" s="144"/>
-      <c r="C6" s="144"/>
-      <c r="D6" s="144"/>
-      <c r="E6" s="144"/>
+      <c r="B6" s="145"/>
+      <c r="C6" s="145"/>
+      <c r="D6" s="145"/>
+      <c r="E6" s="145"/>
     </row>
     <row r="7" spans="1:5" ht="39" customHeight="1">
       <c r="A7" s="18" t="s">
@@ -7617,22 +7625,22 @@
       <c r="E88" s="15"/>
     </row>
     <row r="90" spans="1:5">
-      <c r="A90" s="131" t="s">
+      <c r="A90" s="132" t="s">
         <v>245</v>
       </c>
-      <c r="B90" s="144"/>
-      <c r="C90" s="144"/>
-      <c r="D90" s="144"/>
-      <c r="E90" s="144"/>
+      <c r="B90" s="145"/>
+      <c r="C90" s="145"/>
+      <c r="D90" s="145"/>
+      <c r="E90" s="145"/>
     </row>
     <row r="92" spans="1:5" ht="46.5" customHeight="1">
-      <c r="A92" s="130" t="s">
+      <c r="A92" s="131" t="s">
         <v>223</v>
       </c>
-      <c r="B92" s="143"/>
-      <c r="C92" s="143"/>
-      <c r="D92" s="143"/>
-      <c r="E92" s="143"/>
+      <c r="B92" s="144"/>
+      <c r="C92" s="144"/>
+      <c r="D92" s="144"/>
+      <c r="E92" s="144"/>
     </row>
     <row r="93" spans="1:5">
       <c r="A93" s="12" t="s">
@@ -7693,13 +7701,13 @@
       <c r="E96" s="17"/>
     </row>
     <row r="97" spans="1:5">
-      <c r="A97" s="131" t="s">
+      <c r="A97" s="132" t="s">
         <v>53</v>
       </c>
-      <c r="B97" s="144"/>
-      <c r="C97" s="144"/>
-      <c r="D97" s="144"/>
-      <c r="E97" s="144"/>
+      <c r="B97" s="145"/>
+      <c r="C97" s="145"/>
+      <c r="D97" s="145"/>
+      <c r="E97" s="145"/>
     </row>
     <row r="98" spans="1:5" ht="36">
       <c r="A98" s="18" t="s">
@@ -8772,22 +8780,22 @@
       <c r="E179" s="15"/>
     </row>
     <row r="181" spans="1:5">
-      <c r="A181" s="131" t="s">
+      <c r="A181" s="132" t="s">
         <v>245</v>
       </c>
-      <c r="B181" s="144"/>
-      <c r="C181" s="144"/>
-      <c r="D181" s="144"/>
-      <c r="E181" s="144"/>
+      <c r="B181" s="145"/>
+      <c r="C181" s="145"/>
+      <c r="D181" s="145"/>
+      <c r="E181" s="145"/>
     </row>
     <row r="183" spans="1:5" ht="42" customHeight="1">
-      <c r="A183" s="130" t="s">
+      <c r="A183" s="131" t="s">
         <v>223</v>
       </c>
-      <c r="B183" s="143"/>
-      <c r="C183" s="143"/>
-      <c r="D183" s="143"/>
-      <c r="E183" s="143"/>
+      <c r="B183" s="144"/>
+      <c r="C183" s="144"/>
+      <c r="D183" s="144"/>
+      <c r="E183" s="144"/>
     </row>
     <row r="184" spans="1:5">
       <c r="A184" s="12" t="s">
@@ -8861,13 +8869,13 @@
       <c r="E188" s="17"/>
     </row>
     <row r="189" spans="1:5">
-      <c r="A189" s="131" t="s">
+      <c r="A189" s="132" t="s">
         <v>53</v>
       </c>
-      <c r="B189" s="144"/>
-      <c r="C189" s="144"/>
-      <c r="D189" s="144"/>
-      <c r="E189" s="144"/>
+      <c r="B189" s="145"/>
+      <c r="C189" s="145"/>
+      <c r="D189" s="145"/>
+      <c r="E189" s="145"/>
     </row>
     <row r="190" spans="1:5" ht="36">
       <c r="A190" s="18" t="s">
@@ -9940,22 +9948,22 @@
       <c r="E271" s="15"/>
     </row>
     <row r="273" spans="1:5">
-      <c r="A273" s="131" t="s">
+      <c r="A273" s="132" t="s">
         <v>245</v>
       </c>
-      <c r="B273" s="144"/>
-      <c r="C273" s="144"/>
-      <c r="D273" s="144"/>
-      <c r="E273" s="144"/>
+      <c r="B273" s="145"/>
+      <c r="C273" s="145"/>
+      <c r="D273" s="145"/>
+      <c r="E273" s="145"/>
     </row>
     <row r="275" spans="1:5" ht="52.5" customHeight="1">
-      <c r="A275" s="130" t="s">
+      <c r="A275" s="131" t="s">
         <v>223</v>
       </c>
-      <c r="B275" s="143"/>
-      <c r="C275" s="143"/>
-      <c r="D275" s="143"/>
-      <c r="E275" s="143"/>
+      <c r="B275" s="144"/>
+      <c r="C275" s="144"/>
+      <c r="D275" s="144"/>
+      <c r="E275" s="144"/>
     </row>
     <row r="276" spans="1:5">
       <c r="A276" s="12" t="s">
@@ -10014,13 +10022,13 @@
       <c r="E279" s="17"/>
     </row>
     <row r="280" spans="1:5">
-      <c r="A280" s="131" t="s">
+      <c r="A280" s="132" t="s">
         <v>53</v>
       </c>
-      <c r="B280" s="144"/>
-      <c r="C280" s="144"/>
-      <c r="D280" s="144"/>
-      <c r="E280" s="144"/>
+      <c r="B280" s="145"/>
+      <c r="C280" s="145"/>
+      <c r="D280" s="145"/>
+      <c r="E280" s="145"/>
     </row>
     <row r="281" spans="1:5" ht="36">
       <c r="A281" s="18" t="s">
@@ -11124,13 +11132,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="34.5" customHeight="1">
-      <c r="A1" s="132" t="s">
+      <c r="A1" s="133" t="s">
         <v>388</v>
       </c>
-      <c r="B1" s="133"/>
-      <c r="C1" s="133"/>
-      <c r="D1" s="133"/>
-      <c r="E1" s="133"/>
+      <c r="B1" s="134"/>
+      <c r="C1" s="134"/>
+      <c r="D1" s="134"/>
+      <c r="E1" s="134"/>
     </row>
     <row r="2" spans="1:5" ht="27" customHeight="1">
       <c r="A2" s="26" t="s">
@@ -11200,13 +11208,13 @@
       <c r="E6" s="35"/>
     </row>
     <row r="7" spans="1:5" ht="19.5" customHeight="1">
-      <c r="A7" s="132" t="s">
+      <c r="A7" s="133" t="s">
         <v>396</v>
       </c>
-      <c r="B7" s="133"/>
-      <c r="C7" s="133"/>
-      <c r="D7" s="133"/>
-      <c r="E7" s="133"/>
+      <c r="B7" s="134"/>
+      <c r="C7" s="134"/>
+      <c r="D7" s="134"/>
+      <c r="E7" s="134"/>
     </row>
     <row r="8" spans="1:5" ht="24" customHeight="1">
       <c r="A8" s="26" t="s">
@@ -11316,13 +11324,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="36" customHeight="1">
-      <c r="A1" s="132" t="s">
+      <c r="A1" s="133" t="s">
         <v>413</v>
       </c>
-      <c r="B1" s="133"/>
-      <c r="C1" s="133"/>
-      <c r="D1" s="133"/>
-      <c r="E1" s="133"/>
+      <c r="B1" s="134"/>
+      <c r="C1" s="134"/>
+      <c r="D1" s="134"/>
+      <c r="E1" s="134"/>
     </row>
     <row r="2" spans="1:5" ht="23.25" customHeight="1">
       <c r="A2" s="26" t="s">
@@ -11402,13 +11410,13 @@
       <c r="E6" s="35"/>
     </row>
     <row r="7" spans="1:5" ht="15" customHeight="1">
-      <c r="A7" s="132" t="s">
+      <c r="A7" s="133" t="s">
         <v>420</v>
       </c>
-      <c r="B7" s="133"/>
-      <c r="C7" s="133"/>
-      <c r="D7" s="133"/>
-      <c r="E7" s="133"/>
+      <c r="B7" s="134"/>
+      <c r="C7" s="134"/>
+      <c r="D7" s="134"/>
+      <c r="E7" s="134"/>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="26" t="s">
@@ -11570,13 +11578,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="134" t="s">
+      <c r="A1" s="135" t="s">
         <v>437</v>
       </c>
-      <c r="B1" s="134"/>
-      <c r="C1" s="134"/>
-      <c r="D1" s="134"/>
-      <c r="E1" s="134"/>
+      <c r="B1" s="135"/>
+      <c r="C1" s="135"/>
+      <c r="D1" s="135"/>
+      <c r="E1" s="135"/>
       <c r="F1" s="58"/>
     </row>
     <row r="2" spans="1:6">
@@ -11625,13 +11633,13 @@
       </c>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="135" t="s">
+      <c r="A5" s="136" t="s">
         <v>440</v>
       </c>
-      <c r="B5" s="135"/>
-      <c r="C5" s="135"/>
-      <c r="D5" s="135"/>
-      <c r="E5" s="135"/>
+      <c r="B5" s="136"/>
+      <c r="C5" s="136"/>
+      <c r="D5" s="136"/>
+      <c r="E5" s="136"/>
       <c r="F5" s="64"/>
     </row>
     <row r="6" spans="1:6">
@@ -11759,13 +11767,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="136" t="s">
+      <c r="A1" s="137" t="s">
         <v>451</v>
       </c>
-      <c r="B1" s="137"/>
-      <c r="C1" s="137"/>
-      <c r="D1" s="137"/>
-      <c r="E1" s="138"/>
+      <c r="B1" s="138"/>
+      <c r="C1" s="138"/>
+      <c r="D1" s="138"/>
+      <c r="E1" s="139"/>
       <c r="F1" s="69"/>
       <c r="G1" s="70"/>
     </row>
@@ -11977,14 +11985,14 @@
       <c r="G12" s="88"/>
     </row>
     <row r="13" spans="1:7" ht="15" customHeight="1">
-      <c r="A13" s="139" t="s">
+      <c r="A13" s="140" t="s">
         <v>484</v>
       </c>
-      <c r="B13" s="139"/>
-      <c r="C13" s="139"/>
-      <c r="D13" s="139"/>
-      <c r="E13" s="139"/>
-      <c r="F13" s="140"/>
+      <c r="B13" s="140"/>
+      <c r="C13" s="140"/>
+      <c r="D13" s="140"/>
+      <c r="E13" s="140"/>
+      <c r="F13" s="141"/>
       <c r="G13" s="90"/>
     </row>
     <row r="14" spans="1:7" ht="27">
